--- a/media/exports/reports/2026-09/growth-trades.xlsx
+++ b/media/exports/reports/2026-09/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
     <row r="9" ht="60" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>September's jobs made $96,230 gross margin (42.7%). Technician time not charged to jobs took $28,417 and overheads $59,580, leaving $8,233 profit before tax (3.7% of revenue). To cover overheads, jobs need a 39.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
     <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>$202,337 against $128,255</t>
+          <t>$225,460 against $143,077</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>$574,589 against $454,179</t>
+          <t>$640,593 against $506,783</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>$217,865 before overheads</t>
+          <t>$283,869 before overheads</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Revenue is 26.5% up on the same period last year, year to date ($574,589 against $454,179). Maintenance contracts make the highest gross margin (59.5%); Installations the lowest (29.4%). The business needs 31.1% gross margin just to cover overheads.</t>
+          <t>Revenue is 26.4% up on the same period last year, year to date ($640,593 against $506,783). Maintenance contracts make the highest gross margin (63.9%); Installations the lowest (37.0%). The business needs 39.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Installations: 29.4% gross margin, 5.6 points under the 35.0% target: about $20,473 on $367,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($29,823 ahead on $121,500 this financial year to date).</t>
+          <t>Installations: 37.0% gross margin, 2.0 points over the 35.0% target ($8,257 ahead on $412,100 this financial year to date). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($39,281 ahead on $136,050 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>$40,500 against $33,200</t>
+          <t>$45,350 against $37,200</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>$121,500 against $99,600</t>
+          <t>$136,050 against $111,600</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>$72,348 before overheads</t>
+          <t>$86,898 before overheads</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts brought in $121,500 this financial year to date, 22.0% on the same period last year (slower than the business as a whole, 26.5%), at a 59.5% gross margin (above the 37.9% overall).</t>
+          <t>Maintenance contracts brought in $136,050 this financial year to date, 21.9% on the same period last year (slower than the business as a whole, 26.4%), at a 63.9% gross margin (above the 44.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($29,823 ahead on $121,500 this financial year to date).</t>
+          <t>Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($39,281 ahead on $136,050 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>$130,700 against $75,100</t>
+          <t>$146,300 against $84,200</t>
         </is>
       </c>
     </row>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>$367,900 against $297,100</t>
+          <t>$412,100 against $332,800</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>$108,292 before overheads</t>
+          <t>$152,492 before overheads</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
     <row r="45" ht="45" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Installations brought in $367,900 this financial year to date, 23.8% on the same period last year (slower than the business as a whole, 26.5%), at a 29.4% gross margin (below the 37.9% overall).</t>
+          <t>Installations brought in $412,100 this financial year to date, 23.8% on the same period last year (slower than the business as a whole, 26.4%), at a 37.0% gross margin (below the 44.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 29.4% gross margin, 5.6 points under the 35.0% target: about $20,473 on $367,900 of revenue this financial year to date. It's below the 31.1% needed to cover overheads, too.</t>
+          <t>Installations: 37.0% gross margin, 2.0 points over the 35.0% target ($8,257 ahead on $412,100 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>$31,137 against $19,955</t>
+          <t>$33,810 against $21,677</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>$85,189 against $57,479</t>
+          <t>$92,443 against $62,383</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>$37,225 before overheads</t>
+          <t>$44,479 before overheads</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
     <row r="57" ht="45" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs brought in $85,189 this financial year to date, 48.2% on the same period last year (faster than the business as a whole, 26.5%), at a 43.7% gross margin (above the 37.9% overall).</t>
+          <t>Call-outs and repairs brought in $92,443 this financial year to date, 48.2% on the same period last year (faster than the business as a whole, 26.4%), at a 48.1% gross margin (above the 44.3% overall).</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.7% gross margin, 8.7 points over the 35.0% target ($7,409 ahead on $85,189 this financial year to date).</t>
+          <t>Call-outs and repairs: 48.1% gross margin, 13.1 points over the 35.0% target ($12,124 ahead on $92,443 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1394,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="9">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="10">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="16">
@@ -1506,7 +1506,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="26">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
     </row>
     <row r="27">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>574589</v>
+        <v>640593</v>
       </c>
     </row>
     <row r="34">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="B34" s="12" t="n">
-        <v>454179</v>
+        <v>506783</v>
       </c>
     </row>
     <row r="35">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B36" s="12" t="n">
-        <v>217865</v>
+        <v>283869</v>
       </c>
     </row>
     <row r="37">
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="B43" s="12" t="n">
-        <v>574589</v>
+        <v>640593</v>
       </c>
     </row>
     <row r="44">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="B44" s="12" t="n">
-        <v>454179</v>
+        <v>506783</v>
       </c>
     </row>
     <row r="45">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B46" s="12" t="n">
-        <v>217865</v>
+        <v>283869</v>
       </c>
     </row>
     <row r="47">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="B53" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="54">
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
     </row>
     <row r="55">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B61" s="12" t="n">
-        <v>121500</v>
+        <v>136050</v>
       </c>
     </row>
     <row r="62">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B62" s="12" t="n">
-        <v>99600</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="63">
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="B64" s="12" t="n">
-        <v>72348</v>
+        <v>86898</v>
       </c>
     </row>
     <row r="65">
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B71" s="12" t="n">
-        <v>121500</v>
+        <v>136050</v>
       </c>
     </row>
     <row r="72">
@@ -1889,7 +1889,7 @@
         </is>
       </c>
       <c r="B72" s="12" t="n">
-        <v>99600</v>
+        <v>111600</v>
       </c>
     </row>
     <row r="73">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="B74" s="12" t="n">
-        <v>72348</v>
+        <v>86898</v>
       </c>
     </row>
     <row r="75">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="B81" s="12" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
     </row>
     <row r="82">
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="B82" s="12" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
     </row>
     <row r="83">
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="B89" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
     </row>
     <row r="90">
@@ -2020,7 +2020,7 @@
         </is>
       </c>
       <c r="B90" s="12" t="n">
-        <v>297100</v>
+        <v>332800</v>
       </c>
     </row>
     <row r="91">
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="B92" s="12" t="n">
-        <v>108292</v>
+        <v>152492</v>
       </c>
     </row>
     <row r="93">
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B99" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
     </row>
     <row r="100">
@@ -2096,7 +2096,7 @@
         </is>
       </c>
       <c r="B100" s="12" t="n">
-        <v>297100</v>
+        <v>332800</v>
       </c>
     </row>
     <row r="101">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B102" s="12" t="n">
-        <v>108292</v>
+        <v>152492</v>
       </c>
     </row>
     <row r="103">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="B109" s="12" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
     </row>
     <row r="110">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="B110" s="12" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
     </row>
     <row r="111">
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="B117" s="12" t="n">
-        <v>85189</v>
+        <v>92443</v>
       </c>
     </row>
     <row r="118">
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="B118" s="12" t="n">
-        <v>57479</v>
+        <v>62383</v>
       </c>
     </row>
     <row r="119">
@@ -2248,7 +2248,7 @@
         </is>
       </c>
       <c r="B120" s="12" t="n">
-        <v>37225</v>
+        <v>44479</v>
       </c>
     </row>
     <row r="121">
@@ -2293,7 +2293,7 @@
         </is>
       </c>
       <c r="B127" s="12" t="n">
-        <v>85189</v>
+        <v>92443</v>
       </c>
     </row>
     <row r="128">
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="B128" s="12" t="n">
-        <v>57479</v>
+        <v>62383</v>
       </c>
     </row>
     <row r="129">
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="B130" s="12" t="n">
-        <v>37225</v>
+        <v>44479</v>
       </c>
     </row>
     <row r="131">
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
         </is>
       </c>
       <c r="D6" s="12" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>114334</v>
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="D7" s="12" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="12" t="n">
         <v>113016</v>
@@ -2518,7 +2518,7 @@
         </is>
       </c>
       <c r="D8" s="12" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>85316</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>80742</v>
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="D10" s="12" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>102348</v>
@@ -2611,7 +2611,7 @@
         </is>
       </c>
       <c r="D11" s="12" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>85752</v>
@@ -2642,7 +2642,7 @@
         </is>
       </c>
       <c r="D12" s="12" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>76808</v>
@@ -2673,7 +2673,7 @@
         </is>
       </c>
       <c r="D13" s="12" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>83700</v>
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D14" s="12" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>97584</v>
@@ -2735,7 +2735,7 @@
         </is>
       </c>
       <c r="D15" s="12" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>120326</v>
@@ -2766,7 +2766,7 @@
         </is>
       </c>
       <c r="D16" s="12" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>78258</v>
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="D17" s="12" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>80054</v>
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="D18" s="12" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>79452</v>
@@ -2859,7 +2859,7 @@
         </is>
       </c>
       <c r="D19" s="12" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>115942</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="D20" s="12" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>84626</v>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="D21" s="12" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>106590</v>
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="D22" s="12" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>120662</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>123342</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="D24" s="12" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>96144</v>
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="D25" s="12" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E25" s="12" t="n">
         <v>98858</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="D26" s="12" t="n">
-        <v>173163</v>
+        <v>193032</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>106500</v>
@@ -3107,7 +3107,7 @@
         </is>
       </c>
       <c r="D27" s="12" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>122124</v>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="D28" s="12" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>105370</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="D29" s="12" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>129230</v>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="D30" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>10420</v>
@@ -3231,7 +3231,7 @@
         </is>
       </c>
       <c r="D31" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>10420</v>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="D32" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>10420</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="D33" s="12" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>10420</v>
@@ -3324,7 +3324,7 @@
         </is>
       </c>
       <c r="D34" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E34" s="12" t="n">
         <v>11782</v>
@@ -3355,7 +3355,7 @@
         </is>
       </c>
       <c r="D35" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>11782</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="D36" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>11782</v>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D37" s="12" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>11782</v>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="D38" s="12" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>13446</v>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="D39" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E39" s="12" t="n">
         <v>13446</v>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="D40" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E40" s="12" t="n">
         <v>13446</v>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="D41" s="12" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E41" s="12" t="n">
         <v>13446</v>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="D42" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E42" s="12" t="n">
         <v>14516</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="D43" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>14516</v>
@@ -3634,7 +3634,7 @@
         </is>
       </c>
       <c r="D44" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E44" s="12" t="n">
         <v>14516</v>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="D45" s="12" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E45" s="12" t="n">
         <v>14516</v>
@@ -3696,7 +3696,7 @@
         </is>
       </c>
       <c r="D46" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E46" s="12" t="n">
         <v>15158</v>
@@ -3727,7 +3727,7 @@
         </is>
       </c>
       <c r="D47" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>15158</v>
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="D48" s="12" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>15158</v>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="D49" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>16384</v>
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="D50" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E50" s="12" t="n">
         <v>16384</v>
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="D51" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E51" s="12" t="n">
         <v>16384</v>
@@ -3882,7 +3882,7 @@
         </is>
       </c>
       <c r="D52" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E52" s="12" t="n">
         <v>16384</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="D53" s="12" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>16384</v>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D54" s="12" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>92430</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="D55" s="12" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E55" s="12" t="n">
         <v>89070</v>
@@ -4006,7 +4006,7 @@
         </is>
       </c>
       <c r="D56" s="12" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E56" s="12" t="n">
         <v>59908</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="D57" s="12" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E57" s="12" t="n">
         <v>54678</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="D58" s="12" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E58" s="12" t="n">
         <v>74966</v>
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="D59" s="12" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E59" s="12" t="n">
         <v>61664</v>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D60" s="12" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E60" s="12" t="n">
         <v>52264</v>
@@ -4161,7 +4161,7 @@
         </is>
       </c>
       <c r="D61" s="12" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E61" s="12" t="n">
         <v>59534</v>
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="D62" s="12" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E62" s="12" t="n">
         <v>72976</v>
@@ -4223,7 +4223,7 @@
         </is>
       </c>
       <c r="D63" s="12" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E63" s="12" t="n">
         <v>96920</v>
@@ -4254,7 +4254,7 @@
         </is>
       </c>
       <c r="D64" s="12" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E64" s="12" t="n">
         <v>53590</v>
@@ -4285,7 +4285,7 @@
         </is>
       </c>
       <c r="D65" s="12" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E65" s="12" t="n">
         <v>55440</v>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="D66" s="12" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E66" s="12" t="n">
         <v>52288</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="D67" s="12" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E67" s="12" t="n">
         <v>87174</v>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D68" s="12" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E68" s="12" t="n">
         <v>53408</v>
@@ -4409,7 +4409,7 @@
         </is>
       </c>
       <c r="D69" s="12" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E69" s="12" t="n">
         <v>74216</v>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="D70" s="12" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E70" s="12" t="n">
         <v>88896</v>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="D71" s="12" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E71" s="12" t="n">
         <v>94290</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="D72" s="12" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E72" s="12" t="n">
         <v>68016</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D73" s="12" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E73" s="12" t="n">
         <v>66240</v>
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="D74" s="12" t="n">
-        <v>103200</v>
+        <v>115600</v>
       </c>
       <c r="E74" s="12" t="n">
         <v>73792</v>
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="D75" s="12" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="E75" s="12" t="n">
         <v>91520</v>
@@ -4626,7 +4626,7 @@
         </is>
       </c>
       <c r="D76" s="12" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
       <c r="E76" s="12" t="n">
         <v>72720</v>
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="D77" s="12" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="E77" s="12" t="n">
         <v>95368</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="D78" s="12" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E78" s="12" t="n">
         <v>11484</v>
@@ -4719,7 +4719,7 @@
         </is>
       </c>
       <c r="D79" s="12" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E79" s="12" t="n">
         <v>13526</v>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="D80" s="12" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E80" s="12" t="n">
         <v>14988</v>
@@ -4781,7 +4781,7 @@
         </is>
       </c>
       <c r="D81" s="12" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E81" s="12" t="n">
         <v>15644</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="D82" s="12" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E82" s="12" t="n">
         <v>15600</v>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="D83" s="12" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E83" s="12" t="n">
         <v>12306</v>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="D84" s="12" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E84" s="12" t="n">
         <v>12762</v>
@@ -4905,7 +4905,7 @@
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E85" s="12" t="n">
         <v>12384</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="D86" s="12" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E86" s="12" t="n">
         <v>11162</v>
@@ -4967,7 +4967,7 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E87" s="12" t="n">
         <v>9960</v>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="D88" s="12" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E88" s="12" t="n">
         <v>11222</v>
@@ -5029,7 +5029,7 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E89" s="12" t="n">
         <v>11168</v>
@@ -5060,7 +5060,7 @@
         </is>
       </c>
       <c r="D90" s="12" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E90" s="12" t="n">
         <v>12648</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E91" s="12" t="n">
         <v>14252</v>
@@ -5122,7 +5122,7 @@
         </is>
       </c>
       <c r="D92" s="12" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E92" s="12" t="n">
         <v>16702</v>
@@ -5153,7 +5153,7 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E93" s="12" t="n">
         <v>17858</v>
@@ -5184,7 +5184,7 @@
         </is>
       </c>
       <c r="D94" s="12" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E94" s="12" t="n">
         <v>16608</v>
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E95" s="12" t="n">
         <v>13894</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="D96" s="12" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E96" s="12" t="n">
         <v>12970</v>
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E97" s="12" t="n">
         <v>16234</v>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="D98" s="12" t="n">
-        <v>29463</v>
+        <v>32082</v>
       </c>
       <c r="E98" s="12" t="n">
         <v>16324</v>
@@ -5339,7 +5339,7 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="E99" s="12" t="n">
         <v>14220</v>
@@ -5370,7 +5370,7 @@
         </is>
       </c>
       <c r="D100" s="12" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
       <c r="E100" s="12" t="n">
         <v>16266</v>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
       <c r="E101" s="12" t="n">
         <v>17478</v>
@@ -5421,7 +5421,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5473,7 +5473,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -5517,17 +5517,17 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>121500</v>
+        <v>136050</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>99600</v>
+        <v>111600</v>
       </c>
       <c r="D6" s="13">
         <f>IF(C6=0,"",B6/C6-1)</f>
         <v/>
       </c>
       <c r="E6" s="12" t="n">
-        <v>72348</v>
+        <v>86898</v>
       </c>
       <c r="F6" s="13">
         <f>IF(B6=0,"",E6/B6)</f>
@@ -5541,17 +5541,17 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>367900</v>
+        <v>412100</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>297100</v>
+        <v>332800</v>
       </c>
       <c r="D7" s="13">
         <f>IF(C7=0,"",B7/C7-1)</f>
         <v/>
       </c>
       <c r="E7" s="12" t="n">
-        <v>108292</v>
+        <v>152492</v>
       </c>
       <c r="F7" s="13">
         <f>IF(B7=0,"",E7/B7)</f>
@@ -5565,17 +5565,17 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>85189</v>
+        <v>92443</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>57479</v>
+        <v>62383</v>
       </c>
       <c r="D8" s="13">
         <f>IF(C8=0,"",B8/C8-1)</f>
         <v/>
       </c>
       <c r="E8" s="12" t="n">
-        <v>37225</v>
+        <v>44479</v>
       </c>
       <c r="F8" s="13">
         <f>IF(B8=0,"",E8/B8)</f>
@@ -5589,17 +5589,17 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>574589</v>
+        <v>640593</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>454179</v>
+        <v>506783</v>
       </c>
       <c r="D9" s="13">
         <f>IF(C9=0,"",B9/C9-1)</f>
         <v/>
       </c>
       <c r="E9" s="12" t="n">
-        <v>217865</v>
+        <v>283869</v>
       </c>
       <c r="F9" s="13">
         <f>IF(B9=0,"",E9/B9)</f>
@@ -5612,7 +5612,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-09/growth-trades.xlsx
+++ b/media/exports/reports/2026-09/growth-trades.xlsx
@@ -818,7 +818,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B17" s="9">
-        <f>Workings!B37</f>
+        <f>Workings!B35</f>
         <v/>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="B29" s="9">
-        <f>Workings!B65</f>
+        <f>Workings!B63</f>
         <v/>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B41" s="9">
-        <f>Workings!B93</f>
+        <f>Workings!B91</f>
         <v/>
       </c>
       <c r="C41" s="10" t="inlineStr">
@@ -1224,7 +1224,7 @@
         </is>
       </c>
       <c r="B53" s="9">
-        <f>Workings!B121</f>
+        <f>Workings!B119</f>
         <v/>
       </c>
       <c r="C53" s="10" t="inlineStr">
@@ -1315,7 +1315,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1360,7 +1360,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2397,7 +2397,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5421,7 +5421,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5473,7 +5473,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth-trades.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
